--- a/artfynd/A 62768-2025 artfynd.xlsx
+++ b/artfynd/A 62768-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133301359</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133300825</v>
       </c>
       <c r="B3" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133300434</v>
       </c>
       <c r="B4" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133301592</v>
       </c>
       <c r="B5" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62768-2025 artfynd.xlsx
+++ b/artfynd/A 62768-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133301359</v>
       </c>
       <c r="B2" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133300825</v>
       </c>
       <c r="B3" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>133300434</v>
       </c>
       <c r="B4" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>133301592</v>
       </c>
       <c r="B5" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62768-2025 artfynd.xlsx
+++ b/artfynd/A 62768-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133301359</v>
+        <v>133300434</v>
       </c>
       <c r="B2" t="n">
         <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335582</v>
+        <v>335519</v>
       </c>
       <c r="R2" t="n">
-        <v>6387265</v>
+        <v>6387395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spillkråkehack</t>
+          <t>Rikligt med spillkråkehack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +794,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -899,14 +899,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133300434</v>
+        <v>133300983</v>
       </c>
       <c r="B4" t="n">
         <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335519</v>
+        <v>335582</v>
       </c>
       <c r="R4" t="n">
-        <v>6387395</v>
+        <v>6387265</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med spillkråkehack</t>
+          <t>Spillkråkehack</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62768-2025 artfynd.xlsx
+++ b/artfynd/A 62768-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133300434</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133300825</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133300983</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,8 +1140,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133301592</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>